--- a/Comparativa de métodos.xlsx
+++ b/Comparativa de métodos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8cd99136cfcc98d8/Documentos/FCFM/TesinaMCD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="234" documentId="8_{C35CB4B5-116C-41D5-87A2-C79F50F772C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0641E076-580D-4974-9F61-00FC0D275381}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDDFC119-5A8E-4F87-814A-DE111E131944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="6" xr2:uid="{77093374-A388-4AA4-826D-E897928A4FB5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="6" xr2:uid="{77093374-A388-4AA4-826D-E897928A4FB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2970,10 +2970,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
